--- a/media/Levels/kakeraMapLevelTutorial.xlsx
+++ b/media/Levels/kakeraMapLevelTutorial.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yuuta\OneDrive - 学校法人新潟総合学院 学校法人国際総合学園 学校法人大彦学園\ドキュメント\2024年３月特別授業\BaseCross64\DoctorRemote\media\Levels\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\81806\OneDrive - 学校法人新潟総合学院 学校法人国際総合学園 学校法人大彦学園\ドキュメント\DocterRimoto\DoctorRemote_a\media\Levels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{270019FB-940B-417E-8D31-97613CC2E64A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D5C1168-42A6-48AC-A1C6-D710EDE6073D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{A669E15A-D514-4143-B895-055D763399A4}"/>
+    <workbookView xWindow="2508" yWindow="0" windowWidth="15660" windowHeight="12168" xr2:uid="{A669E15A-D514-4143-B895-055D763399A4}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -11434,31 +11434,31 @@
         <v>1</v>
       </c>
       <c r="W49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF49" s="5">
         <v>1</v>
@@ -11661,31 +11661,31 @@
         <v>1</v>
       </c>
       <c r="W50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF50" s="5">
         <v>1</v>
@@ -11888,31 +11888,31 @@
         <v>1</v>
       </c>
       <c r="W51">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X51">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y51">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z51">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA51">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB51">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC51">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD51">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE51">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF51" s="5">
         <v>1</v>
@@ -12115,31 +12115,31 @@
         <v>1</v>
       </c>
       <c r="W52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF52" s="5">
         <v>1</v>
@@ -12342,31 +12342,31 @@
         <v>1</v>
       </c>
       <c r="W53">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X53">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y53">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z53">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA53">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB53">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC53">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD53">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE53">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF53">
         <v>0</v>
@@ -12569,31 +12569,31 @@
         <v>1</v>
       </c>
       <c r="W54">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X54">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y54">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z54">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA54">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB54">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC54">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD54">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE54">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF54">
         <v>0</v>
@@ -12796,31 +12796,31 @@
         <v>1</v>
       </c>
       <c r="W55">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X55">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y55">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z55">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA55">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB55">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC55">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD55">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE55">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF55">
         <v>0</v>
@@ -13023,31 +13023,31 @@
         <v>1</v>
       </c>
       <c r="W56">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X56">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y56">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z56">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA56">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB56">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC56">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD56">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE56">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF56">
         <v>0</v>
